--- a/config/A2700/Source_Test_A2700M.xlsx
+++ b/config/A2700/Source_Test_A2700M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PNT\61.AI\VisionOCR\config\A2700\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76D37C8-8A63-4664-A50E-1D8E233EFEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699A6D21-5560-43A6-AB13-568C2C9373D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4455" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4593" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4585" uniqueCount="633">
   <si>
     <t>TC_ID</t>
   </si>
@@ -1930,6 +1930,26 @@
   </si>
   <si>
     <t>=0.5 ÷ Expected × 100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A27_SPEC-TC0003-01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOME &gt; VOLTAGE &gt; Fundamental</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>65, 150</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>65,185</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>198 ~ 202; 198 ~ 202; 198 ~ 202; 198 ~ 202</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1937,6 +1957,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1977,7 +2000,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1985,6 +2008,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -6260,7 +6284,7 @@
         <v>225</v>
       </c>
       <c r="G127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H127">
         <v>1</v>
@@ -6286,7 +6310,7 @@
         <v>225</v>
       </c>
       <c r="G129">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H129">
         <v>1</v>
@@ -19163,8 +19187,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>16</v>
+      <c r="A8" s="2" t="s">
+        <v>628</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -19386,14 +19410,14 @@
       <c r="E24" t="s">
         <v>427</v>
       </c>
-      <c r="F24" t="s">
-        <v>430</v>
+      <c r="F24" s="5" t="s">
+        <v>631</v>
       </c>
       <c r="H24">
         <v>0.5</v>
       </c>
-      <c r="I24" t="s">
-        <v>431</v>
+      <c r="I24" s="2" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
@@ -19412,14 +19436,14 @@
       <c r="E26" t="s">
         <v>427</v>
       </c>
-      <c r="F26" t="s">
-        <v>428</v>
+      <c r="F26" s="5" t="s">
+        <v>631</v>
       </c>
       <c r="H26">
         <v>0.5</v>
       </c>
-      <c r="I26" t="s">
-        <v>429</v>
+      <c r="I26" s="2" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
@@ -19438,8 +19462,8 @@
       <c r="E28" t="s">
         <v>427</v>
       </c>
-      <c r="F28" t="s">
-        <v>430</v>
+      <c r="F28" s="2" t="s">
+        <v>630</v>
       </c>
       <c r="H28">
         <v>0.5</v>
@@ -20543,6 +20567,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -21926,8 +21951,8 @@
       <c r="C79" t="s">
         <v>473</v>
       </c>
-      <c r="H79" t="s">
-        <v>484</v>
+      <c r="H79" s="1" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
@@ -22022,20 +22047,6 @@
         <v>482</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A84" t="s">
-        <v>40</v>
-      </c>
-      <c r="B84" t="s">
-        <v>288</v>
-      </c>
-      <c r="C84" t="s">
-        <v>483</v>
-      </c>
-      <c r="H84" t="s">
-        <v>483</v>
-      </c>
-    </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>44</v>
@@ -22046,8 +22057,8 @@
       <c r="C86" t="s">
         <v>473</v>
       </c>
-      <c r="H86" t="s">
-        <v>474</v>
+      <c r="H86" s="1" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
@@ -22142,20 +22153,6 @@
         <v>482</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A91" t="s">
-        <v>44</v>
-      </c>
-      <c r="B91" t="s">
-        <v>289</v>
-      </c>
-      <c r="C91" t="s">
-        <v>483</v>
-      </c>
-      <c r="H91" t="s">
-        <v>483</v>
-      </c>
-    </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>56</v>
@@ -22307,7 +22304,7 @@
         <v>320</v>
       </c>
       <c r="F101">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H101" t="s">
         <v>337</v>
@@ -22330,7 +22327,7 @@
         <v>320</v>
       </c>
       <c r="F102">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H102" t="s">
         <v>487</v>
@@ -22353,7 +22350,7 @@
         <v>320</v>
       </c>
       <c r="F103">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H103" t="s">
         <v>489</v>
@@ -22376,7 +22373,7 @@
         <v>320</v>
       </c>
       <c r="F104">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H104" t="s">
         <v>482</v>
@@ -23509,8 +23506,8 @@
       <c r="I169" t="s">
         <v>492</v>
       </c>
-      <c r="J169" t="s">
-        <v>607</v>
+      <c r="J169" s="2" t="s">
+        <v>632</v>
       </c>
       <c r="L169" t="s">
         <v>391</v>

--- a/config/A2700/Source_Test_A2700M.xlsx
+++ b/config/A2700/Source_Test_A2700M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PNT\61.AI\VisionOCR\config\A2700\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699A6D21-5560-43A6-AB13-568C2C9373D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547E043F-C287-40B5-8F30-65F7D6967FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4585" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4585" uniqueCount="618">
   <si>
     <t>TC_ID</t>
   </si>
@@ -1329,6 +1329,12 @@
     <t>HOME &gt; VOLTAGE &gt; Phase</t>
   </si>
   <si>
+    <t>65,185</t>
+  </si>
+  <si>
+    <t>HOME &gt; VOLTAGE &gt; Fundamental</t>
+  </si>
+  <si>
     <t>CURRENT 화면 이동</t>
   </si>
   <si>
@@ -1452,6 +1458,15 @@
     <t>Required Text</t>
   </si>
   <si>
+    <t>ratio_range</t>
+  </si>
+  <si>
+    <t>ratio_text</t>
+  </si>
+  <si>
+    <t>ratio_unit</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -1503,6 +1518,9 @@
     <t>C</t>
   </si>
   <si>
+    <t>Fundamental Voltage</t>
+  </si>
+  <si>
     <t>Phase Current</t>
   </si>
   <si>
@@ -1512,9 +1530,30 @@
     <t>Demo Test와 동일한 Ratio 범위 판정; 세미콜론 순서는 OCR 표시 순서</t>
   </si>
   <si>
+    <t>0 ~ 0; 0 ~ 0; 0 ~ 0; 0 ~ 0</t>
+  </si>
+  <si>
+    <t>0.3 ~ 0.5; 0.3 ~ 0.5; 0.3 ~ 0.5; 0.3 ~ 0.5</t>
+  </si>
+  <si>
     <t>1.0</t>
   </si>
   <si>
+    <t>0.9 ~ 1.1; 0.9 ~ 1.1; 0.9 ~ 1.1; 0.9 ~ 1.1</t>
+  </si>
+  <si>
+    <t>99 ~ 101; 99 ~ 101; 99 ~ 101; 99 ~ 101</t>
+  </si>
+  <si>
+    <t>199 ~ 201; 199 ~ 201; 199 ~ 201; 199 ~ 201</t>
+  </si>
+  <si>
+    <t>59 ~ 61; 19 ~ 21; 59 ~ 61; 99 ~ 101</t>
+  </si>
+  <si>
+    <t>198 ~ 202; 198 ~ 202; 198 ~ 202; 198 ~ 202</t>
+  </si>
+  <si>
     <t>Active Power</t>
   </si>
   <si>
@@ -1524,9 +1563,6 @@
     <t>22.00</t>
   </si>
   <si>
-    <t>w</t>
-  </si>
-  <si>
     <t>TOTAL 표시값</t>
   </si>
   <si>
@@ -1560,6 +1596,9 @@
     <t>Demo Test와 동일한 Ratio Text OR 판정</t>
   </si>
   <si>
+    <t>LEAD|LAG; LEAD|LAG; LEAD|LAG; LEAD|LAG</t>
+  </si>
+  <si>
     <t>Reverse: 음수 표시 확인. OCR이 - 부호를 놓치면 FAIL 가능</t>
   </si>
   <si>
@@ -1617,9 +1656,6 @@
     <t>K-Factor</t>
   </si>
   <si>
-    <t>Fundamental Voltage</t>
-  </si>
-  <si>
     <t>Max 버튼 없음</t>
   </si>
   <si>
@@ -1629,6 +1665,18 @@
     <t>Unbalance Voltage</t>
   </si>
   <si>
+    <t>라벨 Sequence</t>
+  </si>
+  <si>
+    <t>Sequence</t>
+  </si>
+  <si>
+    <t>라벨 Negative-</t>
+  </si>
+  <si>
+    <t>Negative-</t>
+  </si>
+  <si>
     <t>라벨 NEMA</t>
   </si>
   <si>
@@ -1641,93 +1689,90 @@
     <t>Zero-</t>
   </si>
   <si>
-    <t>라벨 Sequence</t>
-  </si>
-  <si>
-    <t>Sequence</t>
-  </si>
-  <si>
-    <t>라벨 Negative-</t>
-  </si>
-  <si>
-    <t>Negative-</t>
-  </si>
-  <si>
     <t>L-N NEMA 표시값</t>
   </si>
   <si>
+    <t>=0.5 ÷ Expected × 100</t>
+  </si>
+  <si>
+    <t>L-L NEMA 표시값</t>
+  </si>
+  <si>
+    <t>U0 표시값</t>
+  </si>
+  <si>
+    <t>U2 표시값</t>
+  </si>
+  <si>
+    <t>L-N; L-L; U0|UO; U2</t>
+  </si>
+  <si>
+    <t>Unbalance Current</t>
+  </si>
+  <si>
+    <t>Phase NEMA 표시값</t>
+  </si>
+  <si>
+    <t>Phase; U0|UO; U2</t>
+  </si>
+  <si>
+    <t>Voltage Symmetrical</t>
+  </si>
+  <si>
+    <t>화면 라벨 구성 미확인 — 여분 토큰으로 Fixed Text FAIL 가능, 첫 실행 후 조정</t>
+  </si>
+  <si>
+    <t>U1 표시값</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>U0</t>
+  </si>
+  <si>
+    <t>Current Symmetrical</t>
+  </si>
+  <si>
+    <t>화면 라벨 구성 미확인 — 첫 실행 후 조정</t>
+  </si>
+  <si>
+    <t>I1 표시값</t>
+  </si>
+  <si>
+    <t>I1</t>
+  </si>
+  <si>
+    <t>I2 표시값</t>
+  </si>
+  <si>
+    <t>I2</t>
+  </si>
+  <si>
+    <t>I0 표시값</t>
+  </si>
+  <si>
+    <t>I0</t>
+  </si>
+  <si>
     <t>L-N</t>
   </si>
   <si>
-    <t>L-L NEMA 표시값</t>
-  </si>
-  <si>
     <t>L-L</t>
   </si>
   <si>
-    <t>U0 표시값</t>
-  </si>
-  <si>
-    <t>U0</t>
-  </si>
-  <si>
     <t>OCR이 U0를 UO로 읽으면 FAIL 가능</t>
   </si>
   <si>
-    <t>U2 표시값</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>Unbalance Current</t>
-  </si>
-  <si>
-    <t>Phase NEMA 표시값</t>
+    <t>3P3W 화면 구성 미확인 — L-N 표시/라벨이 다르면 첫 실행 후 조정</t>
   </si>
   <si>
     <t>Phase</t>
   </si>
   <si>
-    <t>Voltage Symmetrical</t>
-  </si>
-  <si>
-    <t>화면 라벨 구성 미확인 — 여분 토큰으로 Fixed Text FAIL 가능, 첫 실행 후 조정</t>
-  </si>
-  <si>
-    <t>U1 표시값</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>Current Symmetrical</t>
-  </si>
-  <si>
-    <t>화면 라벨 구성 미확인 — 첫 실행 후 조정</t>
-  </si>
-  <si>
-    <t>I1 표시값</t>
-  </si>
-  <si>
-    <t>I1</t>
-  </si>
-  <si>
-    <t>I2 표시값</t>
-  </si>
-  <si>
-    <t>I2</t>
-  </si>
-  <si>
-    <t>I0 표시값</t>
-  </si>
-  <si>
-    <t>I0</t>
-  </si>
-  <si>
-    <t>3P3W 화면 구성 미확인 — L-N 표시/라벨이 다르면 첫 실행 후 조정</t>
-  </si>
-  <si>
     <t>Voltage Unbalance</t>
   </si>
   <si>
@@ -1797,6 +1842,9 @@
     <t>화면 OCR 판정 기준</t>
   </si>
   <si>
+    <t>Required Text로 고정문자를 판정합니다. Check Name=Ratio이면 ratio_range에 low ~ high를 ;로 구분하고, 텍스트 Ratio는 ratio_text에 A|B를 ;로 구분합니다</t>
+  </si>
+  <si>
     <t>MeasurementModbus</t>
   </si>
   <si>
@@ -1836,121 +1884,7 @@
     <t>45.160 은 이중화에서 첫번째 꺼</t>
   </si>
   <si>
-    <t>ratio_range</t>
-  </si>
-  <si>
-    <t>ratio_text</t>
-  </si>
-  <si>
-    <t>ratio_unit</t>
-  </si>
-  <si>
-    <t>0 ~ 0; 0 ~ 0; 0 ~ 0; 0 ~ 0</t>
-  </si>
-  <si>
-    <t>0.3 ~ 0.5; 0.3 ~ 0.5; 0.3 ~ 0.5; 0.3 ~ 0.5</t>
-  </si>
-  <si>
-    <t>0.9 ~ 1.1; 0.9 ~ 1.1; 0.9 ~ 1.1; 0.9 ~ 1.1</t>
-  </si>
-  <si>
-    <t>99 ~ 101; 99 ~ 101; 99 ~ 101; 99 ~ 101</t>
-  </si>
-  <si>
-    <t>199 ~ 201; 199 ~ 201; 199 ~ 201; 199 ~ 201</t>
-  </si>
-  <si>
-    <t>59 ~ 61; 19 ~ 21; 59 ~ 61; 99 ~ 101</t>
-  </si>
-  <si>
-    <t>LEAD|LAG; LEAD|LAG; LEAD|LAG; LEAD|LAG</t>
-  </si>
-  <si>
-    <t>Required Text로 고정문자를 판정합니다. Check Name=Ratio이면 ratio_range에 low ~ high를 ;로 구분하고, 텍스트 Ratio는 ratio_text에 A|B를 ;로 구분합니다</t>
-  </si>
-  <si>
-    <t>A 표시값</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B 표시값</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>C 표시값</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>L-N; L-L; U0|UO; U2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ratio</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase; U0|UO; U2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>라벨 NEMA</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>라벨 Sequence</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>라벨 Negative-</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unbalance Voltage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>라벨 Zero-</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>L-N NEMA 표시값</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>L-L NEMA 표시값</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>U0 표시값</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>U2 표시값</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>=0.5 ÷ Expected × 100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A27_SPEC-TC0003-01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HOME &gt; VOLTAGE &gt; Fundamental</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>65, 150</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>65,185</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>198 ~ 202; 198 ~ 202; 198 ~ 202; 198 ~ 202</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>w|W</t>
   </si>
 </sst>
 </file>
@@ -1958,7 +1892,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -2007,8 +1941,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3650,6 +3584,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6265,7 +6200,7 @@
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A127" t="s">
+      <c r="A127" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B127">
@@ -11345,7 +11280,8 @@
   <dimension ref="A1:L103"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="19.75" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="25.33203125" customWidth="1"/>
     <col min="4" max="12" width="18" customWidth="1"/>
   </cols>
@@ -13289,10 +13225,10 @@
   <dimension ref="A1:J264"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.58203125" customWidth="1"/>
     <col min="2" max="2" width="25.33203125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="40.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.25" customWidth="1"/>
     <col min="5" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -19188,7 +19124,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>628</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -19411,13 +19347,13 @@
         <v>427</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>631</v>
+        <v>432</v>
       </c>
       <c r="H24">
         <v>0.5</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>629</v>
+        <v>433</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
@@ -19437,13 +19373,13 @@
         <v>427</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>631</v>
+        <v>432</v>
       </c>
       <c r="H26">
         <v>0.5</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>629</v>
+        <v>433</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
@@ -19463,7 +19399,7 @@
         <v>427</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>630</v>
+        <v>430</v>
       </c>
       <c r="H28">
         <v>0.5</v>
@@ -19506,22 +19442,22 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D30" t="s">
         <v>426</v>
       </c>
       <c r="E30" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F30" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H30">
         <v>0.5</v>
       </c>
       <c r="I30" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
@@ -19532,22 +19468,22 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D31" t="s">
         <v>426</v>
       </c>
       <c r="E31" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F31" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H31">
         <v>0.5</v>
       </c>
       <c r="I31" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.45">
@@ -19558,22 +19494,22 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D33" t="s">
         <v>426</v>
       </c>
       <c r="E33" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F33" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H33">
         <v>0.5</v>
       </c>
       <c r="I33" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
@@ -19584,22 +19520,22 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D34" t="s">
         <v>426</v>
       </c>
       <c r="E34" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F34" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H34">
         <v>0.5</v>
       </c>
       <c r="I34" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
@@ -19610,22 +19546,22 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D35" t="s">
         <v>426</v>
       </c>
       <c r="E35" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F35" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H35">
         <v>0.5</v>
       </c>
       <c r="I35" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
@@ -19636,22 +19572,22 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D36" t="s">
         <v>426</v>
       </c>
       <c r="E36" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F36" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H36">
         <v>0.5</v>
       </c>
       <c r="I36" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.45">
@@ -19662,22 +19598,22 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D38" t="s">
         <v>426</v>
       </c>
       <c r="E38" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F38" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H38">
         <v>0.5</v>
       </c>
       <c r="I38" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
@@ -19688,22 +19624,22 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D39" t="s">
         <v>426</v>
       </c>
       <c r="E39" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F39" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H39">
         <v>0.5</v>
       </c>
       <c r="I39" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.45">
@@ -19714,22 +19650,22 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D41" t="s">
         <v>426</v>
       </c>
       <c r="E41" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F41" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H41">
         <v>0.5</v>
       </c>
       <c r="I41" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
@@ -19740,22 +19676,22 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D43" t="s">
         <v>426</v>
       </c>
       <c r="E43" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F43" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H43">
         <v>0.5</v>
       </c>
       <c r="I43" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
@@ -19766,22 +19702,22 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D44" t="s">
         <v>426</v>
       </c>
       <c r="E44" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F44" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H44">
         <v>0.5</v>
       </c>
       <c r="I44" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.45">
@@ -19792,22 +19728,22 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D46" t="s">
         <v>426</v>
       </c>
       <c r="E46" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F46" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H46">
         <v>0.5</v>
       </c>
       <c r="I46" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.45">
@@ -19818,22 +19754,22 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D47" t="s">
         <v>426</v>
       </c>
       <c r="E47" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F47" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H47">
         <v>0.5</v>
       </c>
       <c r="I47" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
@@ -19844,22 +19780,22 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D48" t="s">
         <v>426</v>
       </c>
       <c r="E48" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F48" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H48">
         <v>0.5</v>
       </c>
       <c r="I48" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.45">
@@ -19870,22 +19806,22 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D49" t="s">
         <v>426</v>
       </c>
       <c r="E49" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F49" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H49">
         <v>0.5</v>
       </c>
       <c r="I49" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.45">
@@ -19896,22 +19832,22 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D51" t="s">
         <v>426</v>
       </c>
       <c r="E51" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F51" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H51">
         <v>0.5</v>
       </c>
       <c r="I51" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.45">
@@ -19922,22 +19858,22 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D52" t="s">
         <v>426</v>
       </c>
       <c r="E52" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F52" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H52">
         <v>0.5</v>
       </c>
       <c r="I52" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.45">
@@ -19948,22 +19884,22 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D53" t="s">
         <v>426</v>
       </c>
       <c r="E53" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F53" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H53">
         <v>0.5</v>
       </c>
       <c r="I53" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.45">
@@ -19974,22 +19910,22 @@
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D55" t="s">
         <v>426</v>
       </c>
       <c r="E55" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F55" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H55">
         <v>0.5</v>
       </c>
       <c r="I55" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.45">
@@ -20000,22 +19936,22 @@
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D56" t="s">
         <v>426</v>
       </c>
       <c r="E56" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F56" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H56">
         <v>0.5</v>
       </c>
       <c r="I56" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.45">
@@ -20026,22 +19962,22 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D58" t="s">
         <v>426</v>
       </c>
       <c r="E58" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F58" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H58">
         <v>0.5</v>
       </c>
       <c r="I58" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.45">
@@ -20052,22 +19988,22 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D59" t="s">
         <v>426</v>
       </c>
       <c r="E59" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F59" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H59">
         <v>0.5</v>
       </c>
       <c r="I59" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.45">
@@ -20078,22 +20014,22 @@
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D60" t="s">
         <v>426</v>
       </c>
       <c r="E60" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F60" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H60">
         <v>0.5</v>
       </c>
       <c r="I60" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.45">
@@ -20104,22 +20040,22 @@
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D62" t="s">
         <v>426</v>
       </c>
       <c r="E62" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F62" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H62">
         <v>0.5</v>
       </c>
       <c r="I62" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.45">
@@ -20130,22 +20066,22 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D63" t="s">
         <v>426</v>
       </c>
       <c r="E63" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F63" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H63">
         <v>0.5</v>
       </c>
       <c r="I63" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.45">
@@ -20165,13 +20101,13 @@
         <v>427</v>
       </c>
       <c r="F64" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H64">
         <v>0.5</v>
       </c>
       <c r="I64" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.45">
@@ -20182,22 +20118,22 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D65" t="s">
         <v>426</v>
       </c>
       <c r="E65" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F65" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H65">
         <v>0.5</v>
       </c>
       <c r="I65" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.45">
@@ -20217,13 +20153,13 @@
         <v>427</v>
       </c>
       <c r="F67" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H67">
         <v>0.5</v>
       </c>
       <c r="I67" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.45">
@@ -20234,22 +20170,22 @@
         <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D68" t="s">
         <v>426</v>
       </c>
       <c r="E68" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F68" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H68">
         <v>0.5</v>
       </c>
       <c r="I68" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.45">
@@ -20260,22 +20196,22 @@
         <v>1</v>
       </c>
       <c r="C69" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D69" t="s">
         <v>426</v>
       </c>
       <c r="E69" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F69" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H69">
         <v>0.5</v>
       </c>
       <c r="I69" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.45">
@@ -20286,22 +20222,22 @@
         <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D70" t="s">
         <v>426</v>
       </c>
       <c r="E70" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F70" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H70">
         <v>0.5</v>
       </c>
       <c r="I70" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.45">
@@ -20321,13 +20257,13 @@
         <v>427</v>
       </c>
       <c r="F72" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H72">
         <v>0.5</v>
       </c>
       <c r="I72" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.45">
@@ -20347,13 +20283,13 @@
         <v>427</v>
       </c>
       <c r="F73" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H73">
         <v>0.5</v>
       </c>
       <c r="I73" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.45">
@@ -20373,13 +20309,13 @@
         <v>427</v>
       </c>
       <c r="F74" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H74">
         <v>0.5</v>
       </c>
       <c r="I74" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.45">
@@ -20399,13 +20335,13 @@
         <v>427</v>
       </c>
       <c r="F75" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H75">
         <v>0.5</v>
       </c>
       <c r="I75" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.45">
@@ -20425,13 +20361,13 @@
         <v>427</v>
       </c>
       <c r="F77" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H77">
         <v>0.5</v>
       </c>
       <c r="I77" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.45">
@@ -20442,22 +20378,22 @@
         <v>1</v>
       </c>
       <c r="C78" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D78" t="s">
         <v>426</v>
       </c>
       <c r="E78" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F78" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H78">
         <v>0.5</v>
       </c>
       <c r="I78" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.45">
@@ -20468,22 +20404,22 @@
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D79" t="s">
         <v>426</v>
       </c>
       <c r="E79" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F79" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H79">
         <v>0.5</v>
       </c>
       <c r="I79" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.45">
@@ -20494,22 +20430,22 @@
         <v>1</v>
       </c>
       <c r="C80" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D80" t="s">
         <v>426</v>
       </c>
       <c r="E80" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F80" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H80">
         <v>0.5</v>
       </c>
       <c r="I80" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.45">
@@ -20520,22 +20456,22 @@
         <v>1</v>
       </c>
       <c r="C81" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D81" t="s">
         <v>426</v>
       </c>
       <c r="E81" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F81" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H81">
         <v>0.5</v>
       </c>
       <c r="I81" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.45">
@@ -20546,28 +20482,27 @@
         <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D82" t="s">
         <v>426</v>
       </c>
       <c r="E82" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F82" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H82">
         <v>0.5</v>
       </c>
       <c r="I82" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -20603,22 +20538,22 @@
         <v>317</v>
       </c>
       <c r="G1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I1" t="s">
         <v>5</v>
       </c>
       <c r="J1" t="s">
-        <v>601</v>
+        <v>475</v>
       </c>
       <c r="K1" t="s">
-        <v>602</v>
+        <v>476</v>
       </c>
       <c r="L1" t="s">
-        <v>603</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
@@ -20629,10 +20564,10 @@
         <v>280</v>
       </c>
       <c r="C2" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H2" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
@@ -20643,7 +20578,7 @@
         <v>280</v>
       </c>
       <c r="C3" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D3">
         <v>110</v>
@@ -20655,7 +20590,7 @@
         <v>0.5</v>
       </c>
       <c r="H3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
@@ -20666,7 +20601,7 @@
         <v>280</v>
       </c>
       <c r="C4" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D4">
         <v>110</v>
@@ -20678,7 +20613,7 @@
         <v>0.5</v>
       </c>
       <c r="H4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
@@ -20689,7 +20624,7 @@
         <v>280</v>
       </c>
       <c r="C5" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D5">
         <v>110</v>
@@ -20701,7 +20636,7 @@
         <v>0.5</v>
       </c>
       <c r="H5" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
@@ -20712,7 +20647,7 @@
         <v>280</v>
       </c>
       <c r="C6" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D6">
         <v>110</v>
@@ -20724,7 +20659,7 @@
         <v>0.5</v>
       </c>
       <c r="H6" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
@@ -20735,10 +20670,10 @@
         <v>280</v>
       </c>
       <c r="C7" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H7" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
@@ -20749,10 +20684,10 @@
         <v>281</v>
       </c>
       <c r="C9" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H9" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
@@ -20763,7 +20698,7 @@
         <v>281</v>
       </c>
       <c r="C10" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D10">
         <v>380</v>
@@ -20775,7 +20710,7 @@
         <v>0.5</v>
       </c>
       <c r="H10" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
@@ -20786,7 +20721,7 @@
         <v>281</v>
       </c>
       <c r="C11" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D11">
         <v>380</v>
@@ -20798,7 +20733,7 @@
         <v>0.5</v>
       </c>
       <c r="H11" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
@@ -20809,7 +20744,7 @@
         <v>281</v>
       </c>
       <c r="C12" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D12">
         <v>380</v>
@@ -20821,7 +20756,7 @@
         <v>0.5</v>
       </c>
       <c r="H12" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
@@ -20832,7 +20767,7 @@
         <v>281</v>
       </c>
       <c r="C13" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D13">
         <v>380</v>
@@ -20844,7 +20779,7 @@
         <v>0.5</v>
       </c>
       <c r="H13" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
@@ -20855,10 +20790,10 @@
         <v>281</v>
       </c>
       <c r="C14" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H14" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
@@ -20869,10 +20804,10 @@
         <v>282</v>
       </c>
       <c r="C16" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H16" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
@@ -20883,7 +20818,7 @@
         <v>282</v>
       </c>
       <c r="C17" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D17">
         <v>519.62</v>
@@ -20895,7 +20830,7 @@
         <v>0.5</v>
       </c>
       <c r="H17" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
@@ -20906,7 +20841,7 @@
         <v>282</v>
       </c>
       <c r="C18" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D18">
         <v>519.62</v>
@@ -20918,7 +20853,7 @@
         <v>0.5</v>
       </c>
       <c r="H18" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
@@ -20929,7 +20864,7 @@
         <v>282</v>
       </c>
       <c r="C19" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D19">
         <v>519.62</v>
@@ -20941,7 +20876,7 @@
         <v>0.5</v>
       </c>
       <c r="H19" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
@@ -20952,7 +20887,7 @@
         <v>282</v>
       </c>
       <c r="C20" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D20">
         <v>519.62</v>
@@ -20964,7 +20899,7 @@
         <v>0.5</v>
       </c>
       <c r="H20" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
@@ -20975,10 +20910,10 @@
         <v>282</v>
       </c>
       <c r="C21" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H21" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
@@ -20989,10 +20924,10 @@
         <v>283</v>
       </c>
       <c r="C23" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H23" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
@@ -21003,7 +20938,7 @@
         <v>283</v>
       </c>
       <c r="C24" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D24">
         <v>65</v>
@@ -21026,7 +20961,7 @@
         <v>283</v>
       </c>
       <c r="C25" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D25">
         <v>65</v>
@@ -21038,7 +20973,7 @@
         <v>0.5</v>
       </c>
       <c r="H25" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
@@ -21049,7 +20984,7 @@
         <v>283</v>
       </c>
       <c r="C26" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D26">
         <v>65</v>
@@ -21061,7 +20996,7 @@
         <v>0.5</v>
       </c>
       <c r="H26" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
@@ -21072,7 +21007,7 @@
         <v>283</v>
       </c>
       <c r="C27" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D27">
         <v>65</v>
@@ -21084,7 +21019,7 @@
         <v>0.5</v>
       </c>
       <c r="H27" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
@@ -21095,10 +21030,10 @@
         <v>283</v>
       </c>
       <c r="C28" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H28" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
@@ -21109,10 +21044,10 @@
         <v>284</v>
       </c>
       <c r="C30" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H30" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.45">
@@ -21123,7 +21058,7 @@
         <v>284</v>
       </c>
       <c r="C31" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D31">
         <v>220</v>
@@ -21146,7 +21081,7 @@
         <v>284</v>
       </c>
       <c r="C32" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D32">
         <v>220</v>
@@ -21158,7 +21093,7 @@
         <v>0.5</v>
       </c>
       <c r="H32" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
@@ -21169,7 +21104,7 @@
         <v>284</v>
       </c>
       <c r="C33" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D33">
         <v>220</v>
@@ -21181,7 +21116,7 @@
         <v>0.5</v>
       </c>
       <c r="H33" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
@@ -21192,7 +21127,7 @@
         <v>284</v>
       </c>
       <c r="C34" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D34">
         <v>220</v>
@@ -21204,7 +21139,7 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
@@ -21215,10 +21150,10 @@
         <v>284</v>
       </c>
       <c r="C35" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H35" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
@@ -21229,10 +21164,10 @@
         <v>285</v>
       </c>
       <c r="C37" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H37" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.45">
@@ -21243,7 +21178,7 @@
         <v>285</v>
       </c>
       <c r="C38" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D38">
         <v>300</v>
@@ -21266,7 +21201,7 @@
         <v>285</v>
       </c>
       <c r="C39" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D39">
         <v>300</v>
@@ -21278,7 +21213,7 @@
         <v>0.5</v>
       </c>
       <c r="H39" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.45">
@@ -21289,7 +21224,7 @@
         <v>285</v>
       </c>
       <c r="C40" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D40">
         <v>300</v>
@@ -21301,7 +21236,7 @@
         <v>0.5</v>
       </c>
       <c r="H40" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.45">
@@ -21312,7 +21247,7 @@
         <v>285</v>
       </c>
       <c r="C41" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D41">
         <v>300</v>
@@ -21324,7 +21259,7 @@
         <v>0.5</v>
       </c>
       <c r="H41" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.45">
@@ -21335,10 +21270,10 @@
         <v>285</v>
       </c>
       <c r="C42" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H42" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
@@ -21349,10 +21284,10 @@
         <v>286</v>
       </c>
       <c r="C44" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H44" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
@@ -21363,7 +21298,7 @@
         <v>286</v>
       </c>
       <c r="C45" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D45">
         <v>389.74</v>
@@ -21375,7 +21310,7 @@
         <v>0.5</v>
       </c>
       <c r="H45" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.45">
@@ -21386,7 +21321,7 @@
         <v>286</v>
       </c>
       <c r="C46" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D46">
         <v>407.06</v>
@@ -21398,7 +21333,7 @@
         <v>0.5</v>
       </c>
       <c r="H46" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.45">
@@ -21409,7 +21344,7 @@
         <v>286</v>
       </c>
       <c r="C47" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D47">
         <v>398.5</v>
@@ -21421,7 +21356,7 @@
         <v>0.5</v>
       </c>
       <c r="H47" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.45">
@@ -21432,7 +21367,7 @@
         <v>286</v>
       </c>
       <c r="C48" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D48">
         <v>398.43</v>
@@ -21444,7 +21379,7 @@
         <v>0.5</v>
       </c>
       <c r="H48" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.45">
@@ -21455,10 +21390,10 @@
         <v>286</v>
       </c>
       <c r="C49" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H49" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
@@ -21469,10 +21404,10 @@
         <v>287</v>
       </c>
       <c r="C51" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H51" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
@@ -21483,7 +21418,7 @@
         <v>287</v>
       </c>
       <c r="C52" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D52">
         <v>65</v>
@@ -21506,7 +21441,7 @@
         <v>287</v>
       </c>
       <c r="C53" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D53">
         <v>220</v>
@@ -21518,7 +21453,7 @@
         <v>0.5</v>
       </c>
       <c r="H53" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
@@ -21529,7 +21464,7 @@
         <v>287</v>
       </c>
       <c r="C54" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D54">
         <v>300</v>
@@ -21541,7 +21476,7 @@
         <v>0.5</v>
       </c>
       <c r="H54" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
@@ -21552,7 +21487,7 @@
         <v>287</v>
       </c>
       <c r="C55" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D55">
         <v>195</v>
@@ -21564,7 +21499,7 @@
         <v>0.5</v>
       </c>
       <c r="H55" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
@@ -21575,10 +21510,10 @@
         <v>287</v>
       </c>
       <c r="C56" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H56" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.45">
@@ -21589,10 +21524,10 @@
         <v>288</v>
       </c>
       <c r="C58" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H58" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.45">
@@ -21603,7 +21538,7 @@
         <v>288</v>
       </c>
       <c r="C59" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D59">
         <v>381.05</v>
@@ -21615,7 +21550,7 @@
         <v>0.5</v>
       </c>
       <c r="H59" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.45">
@@ -21626,7 +21561,7 @@
         <v>288</v>
       </c>
       <c r="C60" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D60">
         <v>381.05</v>
@@ -21638,7 +21573,7 @@
         <v>0.5</v>
       </c>
       <c r="H60" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
@@ -21649,7 +21584,7 @@
         <v>288</v>
       </c>
       <c r="C61" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D61">
         <v>381.05</v>
@@ -21661,7 +21596,7 @@
         <v>0.5</v>
       </c>
       <c r="H61" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.45">
@@ -21672,7 +21607,7 @@
         <v>288</v>
       </c>
       <c r="C62" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D62">
         <v>381.05</v>
@@ -21684,7 +21619,7 @@
         <v>0.5</v>
       </c>
       <c r="H62" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.45">
@@ -21695,10 +21630,10 @@
         <v>288</v>
       </c>
       <c r="C63" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H63" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.45">
@@ -21709,10 +21644,10 @@
         <v>288</v>
       </c>
       <c r="C65" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H65" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.45">
@@ -21723,7 +21658,7 @@
         <v>288</v>
       </c>
       <c r="C66" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D66">
         <v>762.1</v>
@@ -21735,7 +21670,7 @@
         <v>0.5</v>
       </c>
       <c r="H66" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.45">
@@ -21746,7 +21681,7 @@
         <v>288</v>
       </c>
       <c r="C67" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D67">
         <v>762.1</v>
@@ -21758,7 +21693,7 @@
         <v>0.5</v>
       </c>
       <c r="H67" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.45">
@@ -21769,7 +21704,7 @@
         <v>288</v>
       </c>
       <c r="C68" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D68">
         <v>762.1</v>
@@ -21781,7 +21716,7 @@
         <v>0.5</v>
       </c>
       <c r="H68" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.45">
@@ -21792,7 +21727,7 @@
         <v>288</v>
       </c>
       <c r="C69" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D69">
         <v>762.1</v>
@@ -21804,7 +21739,7 @@
         <v>0.5</v>
       </c>
       <c r="H69" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.45">
@@ -21815,10 +21750,10 @@
         <v>288</v>
       </c>
       <c r="C70" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H70" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
@@ -21829,10 +21764,10 @@
         <v>288</v>
       </c>
       <c r="C72" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H72" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
@@ -21843,7 +21778,7 @@
         <v>288</v>
       </c>
       <c r="C73" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D73">
         <v>762.1</v>
@@ -21855,7 +21790,7 @@
         <v>0.5</v>
       </c>
       <c r="H73" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
@@ -21866,7 +21801,7 @@
         <v>288</v>
       </c>
       <c r="C74" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D74">
         <v>762.1</v>
@@ -21878,7 +21813,7 @@
         <v>0.5</v>
       </c>
       <c r="H74" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
@@ -21889,7 +21824,7 @@
         <v>288</v>
       </c>
       <c r="C75" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D75">
         <v>762.1</v>
@@ -21901,7 +21836,7 @@
         <v>0.5</v>
       </c>
       <c r="H75" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
@@ -21912,7 +21847,7 @@
         <v>288</v>
       </c>
       <c r="C76" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D76">
         <v>762.1</v>
@@ -21924,7 +21859,7 @@
         <v>0.5</v>
       </c>
       <c r="H76" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
@@ -21935,10 +21870,10 @@
         <v>288</v>
       </c>
       <c r="C77" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H77" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.45">
@@ -21949,10 +21884,10 @@
         <v>288</v>
       </c>
       <c r="C79" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
@@ -21963,7 +21898,7 @@
         <v>288</v>
       </c>
       <c r="C80" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D80">
         <v>220</v>
@@ -21986,7 +21921,7 @@
         <v>288</v>
       </c>
       <c r="C81" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D81">
         <v>220</v>
@@ -21998,7 +21933,7 @@
         <v>0.5</v>
       </c>
       <c r="H81" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
@@ -22009,7 +21944,7 @@
         <v>288</v>
       </c>
       <c r="C82" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D82">
         <v>220</v>
@@ -22021,7 +21956,7 @@
         <v>0.5</v>
       </c>
       <c r="H82" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
@@ -22032,7 +21967,7 @@
         <v>288</v>
       </c>
       <c r="C83" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D83">
         <v>220</v>
@@ -22044,7 +21979,7 @@
         <v>0.5</v>
       </c>
       <c r="H83" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.45">
@@ -22055,10 +21990,10 @@
         <v>289</v>
       </c>
       <c r="C86" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
@@ -22069,7 +22004,7 @@
         <v>289</v>
       </c>
       <c r="C87" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D87">
         <v>380</v>
@@ -22081,7 +22016,7 @@
         <v>0.5</v>
       </c>
       <c r="H87" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.45">
@@ -22092,7 +22027,7 @@
         <v>289</v>
       </c>
       <c r="C88" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D88">
         <v>380</v>
@@ -22104,7 +22039,7 @@
         <v>0.5</v>
       </c>
       <c r="H88" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.45">
@@ -22115,7 +22050,7 @@
         <v>289</v>
       </c>
       <c r="C89" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D89">
         <v>380</v>
@@ -22127,7 +22062,7 @@
         <v>0.5</v>
       </c>
       <c r="H89" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
@@ -22138,7 +22073,7 @@
         <v>289</v>
       </c>
       <c r="C90" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D90">
         <v>380</v>
@@ -22150,7 +22085,7 @@
         <v>0.5</v>
       </c>
       <c r="H90" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
@@ -22161,10 +22096,10 @@
         <v>290</v>
       </c>
       <c r="C93" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H93" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
@@ -22175,7 +22110,7 @@
         <v>290</v>
       </c>
       <c r="C94" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -22198,7 +22133,7 @@
         <v>290</v>
       </c>
       <c r="C95" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -22210,7 +22145,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
@@ -22221,7 +22156,7 @@
         <v>290</v>
       </c>
       <c r="C96" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -22233,7 +22168,7 @@
         <v>0</v>
       </c>
       <c r="H96" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
@@ -22244,7 +22179,7 @@
         <v>290</v>
       </c>
       <c r="C97" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -22256,7 +22191,7 @@
         <v>0</v>
       </c>
       <c r="H97" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
@@ -22267,10 +22202,10 @@
         <v>290</v>
       </c>
       <c r="C98" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H98" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
@@ -22281,10 +22216,10 @@
         <v>291</v>
       </c>
       <c r="C100" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H100" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
@@ -22295,7 +22230,7 @@
         <v>291</v>
       </c>
       <c r="C101" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D101">
         <v>6</v>
@@ -22318,7 +22253,7 @@
         <v>291</v>
       </c>
       <c r="C102" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D102">
         <v>6</v>
@@ -22330,7 +22265,7 @@
         <v>5</v>
       </c>
       <c r="H102" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
@@ -22341,7 +22276,7 @@
         <v>291</v>
       </c>
       <c r="C103" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -22353,7 +22288,7 @@
         <v>5</v>
       </c>
       <c r="H103" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
@@ -22364,7 +22299,7 @@
         <v>291</v>
       </c>
       <c r="C104" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D104">
         <v>6</v>
@@ -22376,7 +22311,7 @@
         <v>5</v>
       </c>
       <c r="H104" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.45">
@@ -22387,10 +22322,10 @@
         <v>291</v>
       </c>
       <c r="C105" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H105" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
@@ -22401,10 +22336,10 @@
         <v>298</v>
       </c>
       <c r="C107" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H107" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
@@ -22415,7 +22350,7 @@
         <v>298</v>
       </c>
       <c r="C108" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -22438,7 +22373,7 @@
         <v>298</v>
       </c>
       <c r="C109" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -22450,7 +22385,7 @@
         <v>0</v>
       </c>
       <c r="H109" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
@@ -22461,7 +22396,7 @@
         <v>298</v>
       </c>
       <c r="C110" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -22473,7 +22408,7 @@
         <v>0</v>
       </c>
       <c r="H110" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
@@ -22484,7 +22419,7 @@
         <v>298</v>
       </c>
       <c r="C111" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -22496,7 +22431,7 @@
         <v>0</v>
       </c>
       <c r="H111" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
@@ -22507,10 +22442,10 @@
         <v>298</v>
       </c>
       <c r="C112" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H112" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.45">
@@ -22521,13 +22456,13 @@
         <v>298</v>
       </c>
       <c r="C113" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I113" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J113" t="s">
-        <v>604</v>
+        <v>499</v>
       </c>
       <c r="L113" t="s">
         <v>391</v>
@@ -22541,10 +22476,10 @@
         <v>299</v>
       </c>
       <c r="C115" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H115" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.45">
@@ -22555,7 +22490,7 @@
         <v>299</v>
       </c>
       <c r="C116" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D116">
         <v>21</v>
@@ -22578,7 +22513,7 @@
         <v>299</v>
       </c>
       <c r="C117" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D117">
         <v>21</v>
@@ -22590,7 +22525,7 @@
         <v>10</v>
       </c>
       <c r="H117" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.45">
@@ -22601,7 +22536,7 @@
         <v>299</v>
       </c>
       <c r="C118" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -22613,7 +22548,7 @@
         <v>10</v>
       </c>
       <c r="H118" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.45">
@@ -22624,7 +22559,7 @@
         <v>299</v>
       </c>
       <c r="C119" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D119">
         <v>21</v>
@@ -22636,7 +22571,7 @@
         <v>10</v>
       </c>
       <c r="H119" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.45">
@@ -22647,10 +22582,10 @@
         <v>299</v>
       </c>
       <c r="C120" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H120" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.45">
@@ -22661,13 +22596,13 @@
         <v>299</v>
       </c>
       <c r="C121" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I121" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J121" t="s">
-        <v>605</v>
+        <v>500</v>
       </c>
       <c r="L121" t="s">
         <v>391</v>
@@ -22681,10 +22616,10 @@
         <v>292</v>
       </c>
       <c r="C123" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H123" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.45">
@@ -22695,7 +22630,7 @@
         <v>292</v>
       </c>
       <c r="C124" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D124">
         <v>50</v>
@@ -22704,7 +22639,7 @@
         <v>345</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="H124" t="s">
         <v>337</v>
@@ -22718,7 +22653,7 @@
         <v>292</v>
       </c>
       <c r="C125" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D125">
         <v>50</v>
@@ -22727,10 +22662,10 @@
         <v>345</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="H125" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.45">
@@ -22741,7 +22676,7 @@
         <v>292</v>
       </c>
       <c r="C126" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D126">
         <v>50</v>
@@ -22750,10 +22685,10 @@
         <v>345</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="H126" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.45">
@@ -22764,7 +22699,7 @@
         <v>292</v>
       </c>
       <c r="C127" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D127">
         <v>50</v>
@@ -22773,10 +22708,10 @@
         <v>345</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="H127" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.45">
@@ -22787,10 +22722,10 @@
         <v>292</v>
       </c>
       <c r="C128" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H128" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.45">
@@ -22801,13 +22736,13 @@
         <v>292</v>
       </c>
       <c r="C129" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I129" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J129" t="s">
-        <v>606</v>
+        <v>502</v>
       </c>
       <c r="L129" t="s">
         <v>391</v>
@@ -22821,10 +22756,10 @@
         <v>293</v>
       </c>
       <c r="C131" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H131" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.45">
@@ -22835,7 +22770,7 @@
         <v>293</v>
       </c>
       <c r="C132" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D132">
         <v>5</v>
@@ -22858,7 +22793,7 @@
         <v>293</v>
       </c>
       <c r="C133" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D133">
         <v>5</v>
@@ -22870,7 +22805,7 @@
         <v>0.2</v>
       </c>
       <c r="H133" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.45">
@@ -22881,7 +22816,7 @@
         <v>293</v>
       </c>
       <c r="C134" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D134">
         <v>5</v>
@@ -22893,7 +22828,7 @@
         <v>0.2</v>
       </c>
       <c r="H134" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.45">
@@ -22904,7 +22839,7 @@
         <v>293</v>
       </c>
       <c r="C135" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D135">
         <v>5</v>
@@ -22916,7 +22851,7 @@
         <v>0.2</v>
       </c>
       <c r="H135" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.45">
@@ -22927,10 +22862,10 @@
         <v>293</v>
       </c>
       <c r="C136" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H136" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.45">
@@ -22941,13 +22876,13 @@
         <v>293</v>
       </c>
       <c r="C137" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I137" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J137" t="s">
-        <v>607</v>
+        <v>503</v>
       </c>
       <c r="L137" t="s">
         <v>391</v>
@@ -22961,10 +22896,10 @@
         <v>294</v>
       </c>
       <c r="C139" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H139" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.45">
@@ -22975,7 +22910,7 @@
         <v>294</v>
       </c>
       <c r="C140" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D140">
         <v>10</v>
@@ -22998,7 +22933,7 @@
         <v>294</v>
       </c>
       <c r="C141" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D141">
         <v>10</v>
@@ -23010,7 +22945,7 @@
         <v>0.2</v>
       </c>
       <c r="H141" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.45">
@@ -23021,7 +22956,7 @@
         <v>294</v>
       </c>
       <c r="C142" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D142">
         <v>10</v>
@@ -23033,7 +22968,7 @@
         <v>0.2</v>
       </c>
       <c r="H142" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.45">
@@ -23044,7 +22979,7 @@
         <v>294</v>
       </c>
       <c r="C143" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D143">
         <v>10</v>
@@ -23056,7 +22991,7 @@
         <v>0.2</v>
       </c>
       <c r="H143" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.45">
@@ -23067,10 +23002,10 @@
         <v>294</v>
       </c>
       <c r="C144" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H144" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.45">
@@ -23081,13 +23016,13 @@
         <v>294</v>
       </c>
       <c r="C145" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I145" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J145" t="s">
-        <v>608</v>
+        <v>504</v>
       </c>
       <c r="L145" t="s">
         <v>391</v>
@@ -23101,10 +23036,10 @@
         <v>295</v>
       </c>
       <c r="C147" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H147" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.45">
@@ -23115,7 +23050,7 @@
         <v>295</v>
       </c>
       <c r="C148" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -23138,7 +23073,7 @@
         <v>295</v>
       </c>
       <c r="C149" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D149">
         <v>3</v>
@@ -23150,7 +23085,7 @@
         <v>0.5</v>
       </c>
       <c r="H149" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.45">
@@ -23161,7 +23096,7 @@
         <v>295</v>
       </c>
       <c r="C150" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D150">
         <v>5</v>
@@ -23173,7 +23108,7 @@
         <v>0.5</v>
       </c>
       <c r="H150" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.45">
@@ -23184,7 +23119,7 @@
         <v>295</v>
       </c>
       <c r="C151" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D151">
         <v>3</v>
@@ -23196,7 +23131,7 @@
         <v>0.5</v>
       </c>
       <c r="H151" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.45">
@@ -23207,10 +23142,10 @@
         <v>295</v>
       </c>
       <c r="C152" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H152" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.45">
@@ -23221,13 +23156,13 @@
         <v>295</v>
       </c>
       <c r="C153" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I153" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J153" t="s">
-        <v>609</v>
+        <v>505</v>
       </c>
       <c r="L153" t="s">
         <v>391</v>
@@ -23241,10 +23176,10 @@
         <v>296</v>
       </c>
       <c r="C155" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H155" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.45">
@@ -23255,7 +23190,7 @@
         <v>296</v>
       </c>
       <c r="C156" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D156">
         <v>5</v>
@@ -23278,7 +23213,7 @@
         <v>296</v>
       </c>
       <c r="C157" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D157">
         <v>5</v>
@@ -23290,7 +23225,7 @@
         <v>0.5</v>
       </c>
       <c r="H157" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.45">
@@ -23301,7 +23236,7 @@
         <v>296</v>
       </c>
       <c r="C158" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D158">
         <v>5</v>
@@ -23313,7 +23248,7 @@
         <v>0.5</v>
       </c>
       <c r="H158" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.45">
@@ -23324,7 +23259,7 @@
         <v>296</v>
       </c>
       <c r="C159" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D159">
         <v>5</v>
@@ -23336,7 +23271,7 @@
         <v>0.5</v>
       </c>
       <c r="H159" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.45">
@@ -23347,10 +23282,10 @@
         <v>296</v>
       </c>
       <c r="C160" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H160" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.45">
@@ -23361,13 +23296,13 @@
         <v>296</v>
       </c>
       <c r="C161" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I161" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J161" t="s">
-        <v>607</v>
+        <v>503</v>
       </c>
       <c r="L161" t="s">
         <v>391</v>
@@ -23381,10 +23316,10 @@
         <v>296</v>
       </c>
       <c r="C163" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H163" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.45">
@@ -23395,7 +23330,7 @@
         <v>296</v>
       </c>
       <c r="C164" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D164">
         <v>10</v>
@@ -23418,7 +23353,7 @@
         <v>296</v>
       </c>
       <c r="C165" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D165">
         <v>10</v>
@@ -23430,7 +23365,7 @@
         <v>0.5</v>
       </c>
       <c r="H165" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.45">
@@ -23441,7 +23376,7 @@
         <v>296</v>
       </c>
       <c r="C166" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D166">
         <v>10</v>
@@ -23453,7 +23388,7 @@
         <v>0.5</v>
       </c>
       <c r="H166" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.45">
@@ -23464,7 +23399,7 @@
         <v>296</v>
       </c>
       <c r="C167" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D167">
         <v>10</v>
@@ -23476,7 +23411,7 @@
         <v>0.5</v>
       </c>
       <c r="H167" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.45">
@@ -23487,10 +23422,10 @@
         <v>296</v>
       </c>
       <c r="C168" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H168" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.45">
@@ -23501,13 +23436,13 @@
         <v>296</v>
       </c>
       <c r="C169" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I169" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>632</v>
+        <v>506</v>
       </c>
       <c r="L169" t="s">
         <v>391</v>
@@ -23521,10 +23456,10 @@
         <v>297</v>
       </c>
       <c r="C171" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H171" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.45">
@@ -23535,7 +23470,7 @@
         <v>297</v>
       </c>
       <c r="C172" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D172">
         <v>5</v>
@@ -23558,7 +23493,7 @@
         <v>297</v>
       </c>
       <c r="C173" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D173">
         <v>5</v>
@@ -23570,7 +23505,7 @@
         <v>0.5</v>
       </c>
       <c r="H173" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.45">
@@ -23581,7 +23516,7 @@
         <v>297</v>
       </c>
       <c r="C174" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D174">
         <v>5</v>
@@ -23593,7 +23528,7 @@
         <v>0.5</v>
       </c>
       <c r="H174" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.45">
@@ -23604,7 +23539,7 @@
         <v>297</v>
       </c>
       <c r="C175" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D175">
         <v>5</v>
@@ -23616,7 +23551,7 @@
         <v>0.5</v>
       </c>
       <c r="H175" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.45">
@@ -23627,10 +23562,10 @@
         <v>297</v>
       </c>
       <c r="C176" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H176" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.45">
@@ -23641,13 +23576,13 @@
         <v>297</v>
       </c>
       <c r="C177" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I177" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J177" t="s">
-        <v>607</v>
+        <v>503</v>
       </c>
       <c r="L177" t="s">
         <v>391</v>
@@ -23661,10 +23596,10 @@
         <v>296</v>
       </c>
       <c r="C179" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H179" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.45">
@@ -23675,7 +23610,7 @@
         <v>296</v>
       </c>
       <c r="C180" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D180">
         <v>5</v>
@@ -23698,7 +23633,7 @@
         <v>296</v>
       </c>
       <c r="C181" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D181">
         <v>5</v>
@@ -23710,7 +23645,7 @@
         <v>0.5</v>
       </c>
       <c r="H181" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.45">
@@ -23721,7 +23656,7 @@
         <v>296</v>
       </c>
       <c r="C182" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D182">
         <v>5</v>
@@ -23733,7 +23668,7 @@
         <v>0.5</v>
       </c>
       <c r="H182" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.45">
@@ -23744,7 +23679,7 @@
         <v>296</v>
       </c>
       <c r="C183" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D183">
         <v>5</v>
@@ -23756,7 +23691,7 @@
         <v>0.5</v>
       </c>
       <c r="H183" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.45">
@@ -23767,10 +23702,10 @@
         <v>296</v>
       </c>
       <c r="C184" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H184" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.45">
@@ -23781,13 +23716,13 @@
         <v>296</v>
       </c>
       <c r="C185" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I185" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J185" t="s">
-        <v>607</v>
+        <v>503</v>
       </c>
       <c r="L185" t="s">
         <v>391</v>
@@ -23801,10 +23736,10 @@
         <v>296</v>
       </c>
       <c r="C187" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H187" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.45">
@@ -23815,7 +23750,7 @@
         <v>296</v>
       </c>
       <c r="C188" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D188">
         <v>5</v>
@@ -23838,7 +23773,7 @@
         <v>296</v>
       </c>
       <c r="C189" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D189">
         <v>5</v>
@@ -23850,7 +23785,7 @@
         <v>0.5</v>
       </c>
       <c r="H189" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.45">
@@ -23861,7 +23796,7 @@
         <v>296</v>
       </c>
       <c r="C190" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D190">
         <v>5</v>
@@ -23873,7 +23808,7 @@
         <v>0.5</v>
       </c>
       <c r="H190" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.45">
@@ -23884,7 +23819,7 @@
         <v>296</v>
       </c>
       <c r="C191" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D191">
         <v>5</v>
@@ -23896,7 +23831,7 @@
         <v>0.5</v>
       </c>
       <c r="H191" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.45">
@@ -23907,10 +23842,10 @@
         <v>296</v>
       </c>
       <c r="C192" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H192" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.45">
@@ -23921,13 +23856,13 @@
         <v>296</v>
       </c>
       <c r="C193" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I193" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J193" t="s">
-        <v>607</v>
+        <v>503</v>
       </c>
       <c r="L193" t="s">
         <v>391</v>
@@ -23941,13 +23876,13 @@
         <v>300</v>
       </c>
       <c r="C195" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H195" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="I195" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.45">
@@ -23958,13 +23893,13 @@
         <v>300</v>
       </c>
       <c r="C196" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="E196" t="s">
-        <v>497</v>
+        <v>617</v>
       </c>
       <c r="F196">
         <v>1</v>
@@ -23981,19 +23916,19 @@
         <v>300</v>
       </c>
       <c r="C197" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="E197" t="s">
-        <v>497</v>
+        <v>617</v>
       </c>
       <c r="F197">
         <v>1</v>
       </c>
       <c r="H197" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.45">
@@ -24004,19 +23939,19 @@
         <v>300</v>
       </c>
       <c r="C198" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="E198" t="s">
-        <v>497</v>
+        <v>617</v>
       </c>
       <c r="F198">
         <v>1</v>
       </c>
       <c r="H198" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.45">
@@ -24027,19 +23962,19 @@
         <v>300</v>
       </c>
       <c r="C199" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="E199" t="s">
-        <v>497</v>
+        <v>617</v>
       </c>
       <c r="F199">
         <v>1</v>
       </c>
       <c r="H199" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.45">
@@ -24050,10 +23985,10 @@
         <v>300</v>
       </c>
       <c r="C200" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H200" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.45">
@@ -24064,13 +23999,13 @@
         <v>300</v>
       </c>
       <c r="C201" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E201" t="s">
         <v>391</v>
       </c>
       <c r="I201" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.45">
@@ -24081,10 +24016,10 @@
         <v>301</v>
       </c>
       <c r="C203" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H203" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.45">
@@ -24095,7 +24030,7 @@
         <v>301</v>
       </c>
       <c r="C204" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D204">
         <v>1.1000000000000001</v>
@@ -24118,7 +24053,7 @@
         <v>301</v>
       </c>
       <c r="C205" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D205">
         <v>1.1000000000000001</v>
@@ -24130,7 +24065,7 @@
         <v>0.5</v>
       </c>
       <c r="H205" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.45">
@@ -24141,7 +24076,7 @@
         <v>301</v>
       </c>
       <c r="C206" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D206">
         <v>1.1000000000000001</v>
@@ -24153,7 +24088,7 @@
         <v>0.5</v>
       </c>
       <c r="H206" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.45">
@@ -24164,7 +24099,7 @@
         <v>301</v>
       </c>
       <c r="C207" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="D207">
         <v>3.3</v>
@@ -24176,7 +24111,7 @@
         <v>0.5</v>
       </c>
       <c r="H207" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.45">
@@ -24187,10 +24122,10 @@
         <v>301</v>
       </c>
       <c r="C208" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H208" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.45">
@@ -24201,13 +24136,13 @@
         <v>301</v>
       </c>
       <c r="C209" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E209" t="s">
         <v>391</v>
       </c>
       <c r="I209" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.45">
@@ -24218,13 +24153,13 @@
         <v>302</v>
       </c>
       <c r="C211" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H211" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="I211" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.45">
@@ -24235,13 +24170,13 @@
         <v>302</v>
       </c>
       <c r="C212" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="E212" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="F212">
         <v>1</v>
@@ -24258,19 +24193,19 @@
         <v>302</v>
       </c>
       <c r="C213" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="E213" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="F213">
         <v>1</v>
       </c>
       <c r="H213" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.45">
@@ -24281,19 +24216,19 @@
         <v>302</v>
       </c>
       <c r="C214" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="E214" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="F214">
         <v>1</v>
       </c>
       <c r="H214" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.45">
@@ -24304,19 +24239,19 @@
         <v>302</v>
       </c>
       <c r="C215" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="E215" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="F215">
         <v>1</v>
       </c>
       <c r="H215" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.45">
@@ -24327,10 +24262,10 @@
         <v>302</v>
       </c>
       <c r="C216" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H216" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.45">
@@ -24341,13 +24276,13 @@
         <v>302</v>
       </c>
       <c r="C217" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E217" t="s">
         <v>391</v>
       </c>
       <c r="I217" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.45">
@@ -24358,10 +24293,10 @@
         <v>303</v>
       </c>
       <c r="C219" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H219" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.45">
@@ -24372,7 +24307,7 @@
         <v>303</v>
       </c>
       <c r="C220" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D220">
         <v>1.1000000000000001</v>
@@ -24395,7 +24330,7 @@
         <v>303</v>
       </c>
       <c r="C221" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D221">
         <v>1.1000000000000001</v>
@@ -24407,7 +24342,7 @@
         <v>0.5</v>
       </c>
       <c r="H221" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.45">
@@ -24418,7 +24353,7 @@
         <v>303</v>
       </c>
       <c r="C222" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D222">
         <v>1.1000000000000001</v>
@@ -24430,7 +24365,7 @@
         <v>0.5</v>
       </c>
       <c r="H222" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.45">
@@ -24441,7 +24376,7 @@
         <v>303</v>
       </c>
       <c r="C223" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="D223">
         <v>3.3</v>
@@ -24453,7 +24388,7 @@
         <v>0.5</v>
       </c>
       <c r="H223" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.45">
@@ -24464,10 +24399,10 @@
         <v>303</v>
       </c>
       <c r="C224" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H224" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.45">
@@ -24478,13 +24413,13 @@
         <v>303</v>
       </c>
       <c r="C225" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E225" t="s">
         <v>391</v>
       </c>
       <c r="I225" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.45">
@@ -24495,10 +24430,10 @@
         <v>304</v>
       </c>
       <c r="C227" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H227" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.45">
@@ -24509,7 +24444,7 @@
         <v>304</v>
       </c>
       <c r="C228" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D228">
         <v>1.1000000000000001</v>
@@ -24532,7 +24467,7 @@
         <v>304</v>
       </c>
       <c r="C229" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D229">
         <v>1.1000000000000001</v>
@@ -24544,7 +24479,7 @@
         <v>0.5</v>
       </c>
       <c r="H229" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.45">
@@ -24555,7 +24490,7 @@
         <v>304</v>
       </c>
       <c r="C230" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D230">
         <v>1.1000000000000001</v>
@@ -24567,7 +24502,7 @@
         <v>0.5</v>
       </c>
       <c r="H230" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.45">
@@ -24578,7 +24513,7 @@
         <v>304</v>
       </c>
       <c r="C231" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="D231">
         <v>3.3</v>
@@ -24590,7 +24525,7 @@
         <v>0.5</v>
       </c>
       <c r="H231" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.45">
@@ -24601,10 +24536,10 @@
         <v>304</v>
       </c>
       <c r="C232" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H232" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.45">
@@ -24615,13 +24550,13 @@
         <v>304</v>
       </c>
       <c r="C233" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E233" t="s">
         <v>391</v>
       </c>
       <c r="I233" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.45">
@@ -24632,10 +24567,10 @@
         <v>304</v>
       </c>
       <c r="C235" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H235" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.45">
@@ -24646,7 +24581,7 @@
         <v>304</v>
       </c>
       <c r="C236" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D236">
         <v>1.1000000000000001</v>
@@ -24669,7 +24604,7 @@
         <v>304</v>
       </c>
       <c r="C237" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D237">
         <v>1.1000000000000001</v>
@@ -24681,7 +24616,7 @@
         <v>0.5</v>
       </c>
       <c r="H237" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.45">
@@ -24692,7 +24627,7 @@
         <v>304</v>
       </c>
       <c r="C238" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D238">
         <v>1.1000000000000001</v>
@@ -24704,7 +24639,7 @@
         <v>0.5</v>
       </c>
       <c r="H238" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.45">
@@ -24715,7 +24650,7 @@
         <v>304</v>
       </c>
       <c r="C239" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="D239">
         <v>3.3</v>
@@ -24727,7 +24662,7 @@
         <v>0.5</v>
       </c>
       <c r="H239" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.45">
@@ -24738,10 +24673,10 @@
         <v>304</v>
       </c>
       <c r="C240" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H240" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.45">
@@ -24752,13 +24687,13 @@
         <v>304</v>
       </c>
       <c r="C241" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E241" t="s">
         <v>391</v>
       </c>
       <c r="I241" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.45">
@@ -24769,10 +24704,10 @@
         <v>304</v>
       </c>
       <c r="C243" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H243" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.45">
@@ -24783,7 +24718,7 @@
         <v>304</v>
       </c>
       <c r="C244" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D244">
         <v>1</v>
@@ -24803,7 +24738,7 @@
         <v>304</v>
       </c>
       <c r="C245" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D245">
         <v>1</v>
@@ -24812,7 +24747,7 @@
         <v>1</v>
       </c>
       <c r="H245" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.45">
@@ -24823,7 +24758,7 @@
         <v>304</v>
       </c>
       <c r="C246" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D246">
         <v>1</v>
@@ -24832,7 +24767,7 @@
         <v>1</v>
       </c>
       <c r="H246" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.45">
@@ -24843,7 +24778,7 @@
         <v>304</v>
       </c>
       <c r="C247" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="D247">
         <v>1</v>
@@ -24852,7 +24787,7 @@
         <v>1</v>
       </c>
       <c r="H247" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.45">
@@ -24863,14 +24798,14 @@
         <v>304</v>
       </c>
       <c r="C248" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="H248" s="2"/>
       <c r="I248" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="K248" t="s">
-        <v>610</v>
+        <v>521</v>
       </c>
     </row>
     <row r="249" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
@@ -24887,10 +24822,10 @@
         <v>304</v>
       </c>
       <c r="C250" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H250" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.45">
@@ -24901,7 +24836,7 @@
         <v>304</v>
       </c>
       <c r="C251" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D251">
         <v>1.1000000000000001</v>
@@ -24924,7 +24859,7 @@
         <v>304</v>
       </c>
       <c r="C252" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D252">
         <v>1.1000000000000001</v>
@@ -24936,7 +24871,7 @@
         <v>0.5</v>
       </c>
       <c r="H252" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.45">
@@ -24947,7 +24882,7 @@
         <v>304</v>
       </c>
       <c r="C253" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D253">
         <v>1.1000000000000001</v>
@@ -24959,7 +24894,7 @@
         <v>0.5</v>
       </c>
       <c r="H253" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.45">
@@ -24970,7 +24905,7 @@
         <v>304</v>
       </c>
       <c r="C254" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="D254">
         <v>3.3</v>
@@ -24982,7 +24917,7 @@
         <v>0.5</v>
       </c>
       <c r="H254" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.45">
@@ -24993,10 +24928,10 @@
         <v>304</v>
       </c>
       <c r="C255" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H255" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.45">
@@ -25007,13 +24942,13 @@
         <v>304</v>
       </c>
       <c r="C256" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E256" t="s">
         <v>391</v>
       </c>
       <c r="I256" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.45">
@@ -25024,13 +24959,13 @@
         <v>304</v>
       </c>
       <c r="C258" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H258" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="I258" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.45">
@@ -25041,7 +24976,7 @@
         <v>304</v>
       </c>
       <c r="C259" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D259">
         <v>-1.1000000000000001</v>
@@ -25064,7 +24999,7 @@
         <v>304</v>
       </c>
       <c r="C260" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D260">
         <v>-1.1000000000000001</v>
@@ -25076,7 +25011,7 @@
         <v>0.5</v>
       </c>
       <c r="H260" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.45">
@@ -25087,7 +25022,7 @@
         <v>304</v>
       </c>
       <c r="C261" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D261">
         <v>-1.1000000000000001</v>
@@ -25099,7 +25034,7 @@
         <v>0.5</v>
       </c>
       <c r="H261" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.45">
@@ -25110,7 +25045,7 @@
         <v>304</v>
       </c>
       <c r="C262" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="D262">
         <v>-3.3</v>
@@ -25122,7 +25057,7 @@
         <v>0.5</v>
       </c>
       <c r="H262" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.45">
@@ -25133,10 +25068,10 @@
         <v>304</v>
       </c>
       <c r="C263" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H263" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.45">
@@ -25147,13 +25082,13 @@
         <v>304</v>
       </c>
       <c r="C264" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E264" t="s">
         <v>391</v>
       </c>
       <c r="I264" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.45">
@@ -25161,13 +25096,13 @@
         <v>152</v>
       </c>
       <c r="C266" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H266" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="I266" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.45">
@@ -25175,7 +25110,7 @@
         <v>152</v>
       </c>
       <c r="C267" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="D267">
         <v>12345</v>
@@ -25187,7 +25122,7 @@
         <v>0</v>
       </c>
       <c r="H267" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.45">
@@ -25195,7 +25130,7 @@
         <v>152</v>
       </c>
       <c r="C268" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="D268">
         <v>23456</v>
@@ -25207,7 +25142,7 @@
         <v>0</v>
       </c>
       <c r="H268" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.45">
@@ -25215,7 +25150,7 @@
         <v>152</v>
       </c>
       <c r="C269" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="D269">
         <v>-11111</v>
@@ -25227,7 +25162,7 @@
         <v>0</v>
       </c>
       <c r="H269" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.45">
@@ -25235,7 +25170,7 @@
         <v>152</v>
       </c>
       <c r="C270" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="D270">
         <v>35801</v>
@@ -25247,7 +25182,7 @@
         <v>0</v>
       </c>
       <c r="H270" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.45">
@@ -25255,13 +25190,13 @@
         <v>156</v>
       </c>
       <c r="C272" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H272" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="I272" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.45">
@@ -25269,7 +25204,7 @@
         <v>156</v>
       </c>
       <c r="C273" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="D273">
         <v>34567</v>
@@ -25281,7 +25216,7 @@
         <v>0</v>
       </c>
       <c r="H273" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.45">
@@ -25289,7 +25224,7 @@
         <v>156</v>
       </c>
       <c r="C274" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="D274">
         <v>45678</v>
@@ -25301,7 +25236,7 @@
         <v>0</v>
       </c>
       <c r="H274" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.45">
@@ -25309,7 +25244,7 @@
         <v>156</v>
       </c>
       <c r="C275" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="D275">
         <v>-11111</v>
@@ -25321,7 +25256,7 @@
         <v>0</v>
       </c>
       <c r="H275" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.45">
@@ -25329,7 +25264,7 @@
         <v>156</v>
       </c>
       <c r="C276" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="D276">
         <v>80245</v>
@@ -25341,7 +25276,7 @@
         <v>0</v>
       </c>
       <c r="H276" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.45">
@@ -25349,13 +25284,13 @@
         <v>159</v>
       </c>
       <c r="C278" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H278" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="I278" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.45">
@@ -25363,7 +25298,7 @@
         <v>159</v>
       </c>
       <c r="C279" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="D279">
         <v>56789</v>
@@ -25378,7 +25313,7 @@
         <v>366</v>
       </c>
       <c r="I279" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.45">
@@ -25389,10 +25324,10 @@
         <v>305</v>
       </c>
       <c r="C281" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H281" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.45">
@@ -25403,7 +25338,7 @@
         <v>305</v>
       </c>
       <c r="C282" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D282">
         <v>1.4139999999999999</v>
@@ -25423,7 +25358,7 @@
         <v>305</v>
       </c>
       <c r="C283" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D283">
         <v>1.4139999999999999</v>
@@ -25432,7 +25367,7 @@
         <v>1.5</v>
       </c>
       <c r="H283" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.45">
@@ -25443,7 +25378,7 @@
         <v>305</v>
       </c>
       <c r="C284" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D284">
         <v>1.4139999999999999</v>
@@ -25452,7 +25387,7 @@
         <v>1.5</v>
       </c>
       <c r="H284" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.45">
@@ -25463,10 +25398,10 @@
         <v>305</v>
       </c>
       <c r="C285" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H285" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.45">
@@ -25477,10 +25412,10 @@
         <v>305</v>
       </c>
       <c r="C287" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H287" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.45">
@@ -25491,7 +25426,7 @@
         <v>305</v>
       </c>
       <c r="C288" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D288">
         <v>1</v>
@@ -25511,7 +25446,7 @@
         <v>305</v>
       </c>
       <c r="C289" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D289">
         <v>1</v>
@@ -25520,7 +25455,7 @@
         <v>2</v>
       </c>
       <c r="H289" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.45">
@@ -25531,7 +25466,7 @@
         <v>305</v>
       </c>
       <c r="C290" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D290">
         <v>1</v>
@@ -25540,7 +25475,7 @@
         <v>2</v>
       </c>
       <c r="H290" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.45">
@@ -25551,10 +25486,10 @@
         <v>305</v>
       </c>
       <c r="C291" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H291" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.45">
@@ -25565,13 +25500,13 @@
         <v>305</v>
       </c>
       <c r="C293" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H293" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="I293" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.45">
@@ -25582,7 +25517,7 @@
         <v>305</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>612</v>
+        <v>490</v>
       </c>
       <c r="D294">
         <v>220</v>
@@ -25594,7 +25529,7 @@
         <v>0.5</v>
       </c>
       <c r="H294" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.45">
@@ -25605,7 +25540,7 @@
         <v>305</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>613</v>
+        <v>491</v>
       </c>
       <c r="D295">
         <v>220</v>
@@ -25617,7 +25552,7 @@
         <v>0.5</v>
       </c>
       <c r="H295" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.45">
@@ -25628,7 +25563,7 @@
         <v>305</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>614</v>
+        <v>493</v>
       </c>
       <c r="D296">
         <v>220</v>
@@ -25640,7 +25575,7 @@
         <v>0.5</v>
       </c>
       <c r="H296" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.45">
@@ -25651,7 +25586,7 @@
         <v>305</v>
       </c>
       <c r="C297" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D297">
         <v>220</v>
@@ -25663,7 +25598,7 @@
         <v>0.5</v>
       </c>
       <c r="H297" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.45">
@@ -25674,13 +25609,13 @@
         <v>305</v>
       </c>
       <c r="C299" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H299" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="I299" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.45">
@@ -25691,7 +25626,7 @@
         <v>305</v>
       </c>
       <c r="C300" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D300">
         <v>5</v>
@@ -25714,7 +25649,7 @@
         <v>305</v>
       </c>
       <c r="C301" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D301">
         <v>5</v>
@@ -25726,7 +25661,7 @@
         <v>0.5</v>
       </c>
       <c r="H301" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.45">
@@ -25737,7 +25672,7 @@
         <v>305</v>
       </c>
       <c r="C302" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D302">
         <v>5</v>
@@ -25749,7 +25684,7 @@
         <v>0.5</v>
       </c>
       <c r="H302" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.45">
@@ -25760,7 +25695,7 @@
         <v>305</v>
       </c>
       <c r="C303" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D303">
         <v>5</v>
@@ -25772,7 +25707,7 @@
         <v>0.5</v>
       </c>
       <c r="H303" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.45">
@@ -25783,13 +25718,13 @@
         <v>305</v>
       </c>
       <c r="C304" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I304" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J304" t="s">
-        <v>607</v>
+        <v>503</v>
       </c>
       <c r="L304" t="s">
         <v>391</v>
@@ -25803,10 +25738,10 @@
         <v>306</v>
       </c>
       <c r="C306" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>621</v>
+        <v>543</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.45">
@@ -25817,10 +25752,10 @@
         <v>306</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>619</v>
+        <v>544</v>
       </c>
       <c r="H307" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.45">
@@ -25831,10 +25766,10 @@
         <v>306</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>620</v>
+        <v>546</v>
       </c>
       <c r="H308" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.45">
@@ -25845,10 +25780,10 @@
         <v>306</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>619</v>
+        <v>544</v>
       </c>
       <c r="H309" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.45">
@@ -25859,10 +25794,10 @@
         <v>306</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.45">
@@ -25873,10 +25808,10 @@
         <v>306</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>618</v>
+        <v>548</v>
       </c>
       <c r="H311" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="312" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
@@ -25887,10 +25822,10 @@
         <v>306</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>622</v>
+        <v>550</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
     </row>
     <row r="313" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
@@ -25901,10 +25836,10 @@
         <v>306</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="K313" s="2"/>
     </row>
@@ -25916,7 +25851,7 @@
         <v>306</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>623</v>
+        <v>552</v>
       </c>
       <c r="D314" s="1">
         <v>4.55</v>
@@ -25929,7 +25864,7 @@
       </c>
       <c r="H314" s="2"/>
       <c r="I314" s="4" t="s">
-        <v>627</v>
+        <v>553</v>
       </c>
       <c r="K314" s="2"/>
     </row>
@@ -25941,7 +25876,7 @@
         <v>306</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>624</v>
+        <v>554</v>
       </c>
       <c r="D315" s="1">
         <v>2.2799999999999998</v>
@@ -25963,7 +25898,7 @@
         <v>306</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="D316" s="1">
         <v>2.62</v>
@@ -25985,7 +25920,7 @@
         <v>306</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>626</v>
+        <v>556</v>
       </c>
       <c r="D317" s="1">
         <v>2.62</v>
@@ -26007,11 +25942,11 @@
         <v>306</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>616</v>
+        <v>497</v>
       </c>
       <c r="H318" s="2"/>
       <c r="K318" s="2" t="s">
-        <v>615</v>
+        <v>557</v>
       </c>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.45">
@@ -26022,10 +25957,10 @@
         <v>307</v>
       </c>
       <c r="C320" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H320" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.45">
@@ -26036,10 +25971,10 @@
         <v>307</v>
       </c>
       <c r="C321" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H321" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.45">
@@ -26050,10 +25985,10 @@
         <v>307</v>
       </c>
       <c r="C322" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="H322" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.45">
@@ -26064,10 +25999,10 @@
         <v>307</v>
       </c>
       <c r="C323" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H323" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.45">
@@ -26078,10 +26013,10 @@
         <v>307</v>
       </c>
       <c r="C324" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="H324" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.45">
@@ -26092,10 +26027,10 @@
         <v>307</v>
       </c>
       <c r="C325" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H325" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.45">
@@ -26106,10 +26041,10 @@
         <v>307</v>
       </c>
       <c r="C326" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H326" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.45">
@@ -26120,7 +26055,7 @@
         <v>307</v>
       </c>
       <c r="C327" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="D327">
         <v>10</v>
@@ -26140,7 +26075,7 @@
         <v>307</v>
       </c>
       <c r="C328" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D328">
         <v>5.77</v>
@@ -26160,7 +26095,7 @@
         <v>307</v>
       </c>
       <c r="C329" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D329">
         <v>5.77</v>
@@ -26180,10 +26115,10 @@
         <v>307</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>616</v>
+        <v>497</v>
       </c>
       <c r="K330" s="2" t="s">
-        <v>617</v>
+        <v>560</v>
       </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.45">
@@ -26194,13 +26129,13 @@
         <v>308</v>
       </c>
       <c r="C332" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H332" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="I332" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.45">
@@ -26211,7 +26146,7 @@
         <v>308</v>
       </c>
       <c r="C333" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="D333">
         <v>213.33</v>
@@ -26223,7 +26158,7 @@
         <v>1</v>
       </c>
       <c r="H333" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.45">
@@ -26234,7 +26169,7 @@
         <v>308</v>
       </c>
       <c r="C334" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D334">
         <v>6.67</v>
@@ -26246,7 +26181,7 @@
         <v>22</v>
       </c>
       <c r="H334" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.45">
@@ -26257,7 +26192,7 @@
         <v>308</v>
       </c>
       <c r="C335" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D335">
         <v>6.67</v>
@@ -26269,7 +26204,7 @@
         <v>22</v>
       </c>
       <c r="H335" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.45">
@@ -26280,13 +26215,13 @@
         <v>309</v>
       </c>
       <c r="C337" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H337" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="I337" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.45">
@@ -26297,7 +26232,7 @@
         <v>309</v>
       </c>
       <c r="C338" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="D338">
         <v>4.67</v>
@@ -26309,7 +26244,7 @@
         <v>1</v>
       </c>
       <c r="H338" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.45">
@@ -26320,7 +26255,7 @@
         <v>309</v>
       </c>
       <c r="C339" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="D339">
         <v>0.33</v>
@@ -26332,7 +26267,7 @@
         <v>25</v>
       </c>
       <c r="H339" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.45">
@@ -26343,7 +26278,7 @@
         <v>309</v>
       </c>
       <c r="C340" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="D340">
         <v>0.33</v>
@@ -26355,7 +26290,7 @@
         <v>25</v>
       </c>
       <c r="H340" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.45">
@@ -26366,10 +26301,10 @@
         <v>308</v>
       </c>
       <c r="C342" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H342" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.45">
@@ -26380,10 +26315,10 @@
         <v>308</v>
       </c>
       <c r="C343" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H343" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.45">
@@ -26394,10 +26329,10 @@
         <v>308</v>
       </c>
       <c r="C344" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H344" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.45">
@@ -26408,10 +26343,10 @@
         <v>308</v>
       </c>
       <c r="C345" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="H345" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.45">
@@ -26422,10 +26357,10 @@
         <v>308</v>
       </c>
       <c r="C346" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H346" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.45">
@@ -26436,10 +26371,10 @@
         <v>308</v>
       </c>
       <c r="C347" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="H347" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.45">
@@ -26450,10 +26385,10 @@
         <v>308</v>
       </c>
       <c r="C348" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H348" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.45">
@@ -26464,10 +26399,10 @@
         <v>308</v>
       </c>
       <c r="C349" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H349" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.45">
@@ -26478,7 +26413,7 @@
         <v>308</v>
       </c>
       <c r="C350" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D350">
         <v>6.25</v>
@@ -26490,7 +26425,7 @@
         <v>15</v>
       </c>
       <c r="H350" t="s">
-        <v>541</v>
+        <v>575</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.45">
@@ -26501,7 +26436,7 @@
         <v>308</v>
       </c>
       <c r="C351" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D351">
         <v>3.1</v>
@@ -26513,7 +26448,7 @@
         <v>15</v>
       </c>
       <c r="H351" t="s">
-        <v>543</v>
+        <v>576</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.45">
@@ -26524,7 +26459,7 @@
         <v>308</v>
       </c>
       <c r="C352" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D352">
         <v>3.13</v>
@@ -26536,10 +26471,10 @@
         <v>25</v>
       </c>
       <c r="H352" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="I352" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.45">
@@ -26550,7 +26485,7 @@
         <v>308</v>
       </c>
       <c r="C353" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D353">
         <v>3.13</v>
@@ -26562,7 +26497,7 @@
         <v>25</v>
       </c>
       <c r="H353" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.45">
@@ -26573,10 +26508,10 @@
         <v>306</v>
       </c>
       <c r="C355" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H355" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.45">
@@ -26587,10 +26522,10 @@
         <v>306</v>
       </c>
       <c r="C356" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H356" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.45">
@@ -26601,10 +26536,10 @@
         <v>306</v>
       </c>
       <c r="C357" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H357" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.45">
@@ -26615,10 +26550,10 @@
         <v>306</v>
       </c>
       <c r="C358" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="H358" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.45">
@@ -26629,10 +26564,10 @@
         <v>306</v>
       </c>
       <c r="C359" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H359" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.45">
@@ -26643,10 +26578,10 @@
         <v>306</v>
       </c>
       <c r="C360" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="H360" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.45">
@@ -26657,10 +26592,10 @@
         <v>306</v>
       </c>
       <c r="C361" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H361" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.45">
@@ -26671,10 +26606,10 @@
         <v>306</v>
       </c>
       <c r="C362" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H362" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.45">
@@ -26685,7 +26620,7 @@
         <v>306</v>
       </c>
       <c r="C363" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D363">
         <v>4.55</v>
@@ -26697,7 +26632,7 @@
         <v>11</v>
       </c>
       <c r="H363" t="s">
-        <v>541</v>
+        <v>575</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.45">
@@ -26708,7 +26643,7 @@
         <v>306</v>
       </c>
       <c r="C364" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D364">
         <v>2.2799999999999998</v>
@@ -26720,7 +26655,7 @@
         <v>15</v>
       </c>
       <c r="H364" t="s">
-        <v>543</v>
+        <v>576</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.45">
@@ -26731,7 +26666,7 @@
         <v>306</v>
       </c>
       <c r="C365" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D365">
         <v>2.62</v>
@@ -26743,10 +26678,10 @@
         <v>25</v>
       </c>
       <c r="H365" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="I365" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.45">
@@ -26757,7 +26692,7 @@
         <v>306</v>
       </c>
       <c r="C366" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D366">
         <v>2.62</v>
@@ -26769,7 +26704,7 @@
         <v>25</v>
       </c>
       <c r="H366" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.45">
@@ -26780,13 +26715,13 @@
         <v>306</v>
       </c>
       <c r="C368" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H368" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="I368" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.45">
@@ -26797,10 +26732,10 @@
         <v>306</v>
       </c>
       <c r="C369" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H369" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.45">
@@ -26811,10 +26746,10 @@
         <v>306</v>
       </c>
       <c r="C370" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H370" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.45">
@@ -26825,10 +26760,10 @@
         <v>306</v>
       </c>
       <c r="C371" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="H371" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.45">
@@ -26839,10 +26774,10 @@
         <v>306</v>
       </c>
       <c r="C372" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H372" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.45">
@@ -26853,10 +26788,10 @@
         <v>306</v>
       </c>
       <c r="C373" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="H373" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.45">
@@ -26867,10 +26802,10 @@
         <v>306</v>
       </c>
       <c r="C374" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H374" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.45">
@@ -26881,10 +26816,10 @@
         <v>306</v>
       </c>
       <c r="C375" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H375" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.45">
@@ -26895,7 +26830,7 @@
         <v>306</v>
       </c>
       <c r="C376" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D376">
         <v>2.2799999999999998</v>
@@ -26907,7 +26842,7 @@
         <v>15</v>
       </c>
       <c r="H376" t="s">
-        <v>543</v>
+        <v>576</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.45">
@@ -26918,7 +26853,7 @@
         <v>306</v>
       </c>
       <c r="C377" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D377">
         <v>2.62</v>
@@ -26930,10 +26865,10 @@
         <v>25</v>
       </c>
       <c r="H377" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="I377" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.45">
@@ -26944,7 +26879,7 @@
         <v>306</v>
       </c>
       <c r="C378" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D378">
         <v>2.62</v>
@@ -26956,7 +26891,7 @@
         <v>25</v>
       </c>
       <c r="H378" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.45">
@@ -26967,10 +26902,10 @@
         <v>310</v>
       </c>
       <c r="C380" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H380" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.45">
@@ -26981,10 +26916,10 @@
         <v>310</v>
       </c>
       <c r="C381" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H381" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.45">
@@ -26995,10 +26930,10 @@
         <v>310</v>
       </c>
       <c r="C382" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H382" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.45">
@@ -27009,10 +26944,10 @@
         <v>310</v>
       </c>
       <c r="C383" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="H383" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.45">
@@ -27023,10 +26958,10 @@
         <v>310</v>
       </c>
       <c r="C384" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H384" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.45">
@@ -27037,10 +26972,10 @@
         <v>310</v>
       </c>
       <c r="C385" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="H385" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.45">
@@ -27051,10 +26986,10 @@
         <v>310</v>
       </c>
       <c r="C386" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H386" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.45">
@@ -27065,10 +27000,10 @@
         <v>310</v>
       </c>
       <c r="C387" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H387" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.45">
@@ -27079,7 +27014,7 @@
         <v>310</v>
       </c>
       <c r="C388" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D388">
         <v>4.55</v>
@@ -27091,7 +27026,7 @@
         <v>11</v>
       </c>
       <c r="H388" t="s">
-        <v>541</v>
+        <v>575</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.45">
@@ -27102,7 +27037,7 @@
         <v>310</v>
       </c>
       <c r="C389" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D389">
         <v>2.2799999999999998</v>
@@ -27114,7 +27049,7 @@
         <v>15</v>
       </c>
       <c r="H389" t="s">
-        <v>543</v>
+        <v>576</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.45">
@@ -27125,7 +27060,7 @@
         <v>310</v>
       </c>
       <c r="C390" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D390">
         <v>2.62</v>
@@ -27137,10 +27072,10 @@
         <v>25</v>
       </c>
       <c r="H390" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="I390" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.45">
@@ -27151,7 +27086,7 @@
         <v>310</v>
       </c>
       <c r="C391" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D391">
         <v>2.62</v>
@@ -27163,7 +27098,7 @@
         <v>25</v>
       </c>
       <c r="H391" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.45">
@@ -27174,10 +27109,10 @@
         <v>311</v>
       </c>
       <c r="C393" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H393" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.45">
@@ -27188,10 +27123,10 @@
         <v>311</v>
       </c>
       <c r="C394" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H394" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.45">
@@ -27202,10 +27137,10 @@
         <v>311</v>
       </c>
       <c r="C395" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H395" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.45">
@@ -27216,10 +27151,10 @@
         <v>311</v>
       </c>
       <c r="C396" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="H396" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.45">
@@ -27230,10 +27165,10 @@
         <v>311</v>
       </c>
       <c r="C397" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H397" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.45">
@@ -27244,10 +27179,10 @@
         <v>311</v>
       </c>
       <c r="C398" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="H398" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.45">
@@ -27258,10 +27193,10 @@
         <v>311</v>
       </c>
       <c r="C399" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H399" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.45">
@@ -27272,10 +27207,10 @@
         <v>311</v>
       </c>
       <c r="C400" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H400" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.45">
@@ -27286,7 +27221,7 @@
         <v>311</v>
       </c>
       <c r="C401" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D401">
         <v>6.25</v>
@@ -27298,7 +27233,7 @@
         <v>15</v>
       </c>
       <c r="H401" t="s">
-        <v>541</v>
+        <v>575</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.45">
@@ -27309,7 +27244,7 @@
         <v>311</v>
       </c>
       <c r="C402" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D402">
         <v>3.1</v>
@@ -27321,7 +27256,7 @@
         <v>15</v>
       </c>
       <c r="H402" t="s">
-        <v>543</v>
+        <v>576</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.45">
@@ -27332,7 +27267,7 @@
         <v>311</v>
       </c>
       <c r="C403" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D403">
         <v>3.13</v>
@@ -27344,10 +27279,10 @@
         <v>25</v>
       </c>
       <c r="H403" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="I403" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.45">
@@ -27358,7 +27293,7 @@
         <v>311</v>
       </c>
       <c r="C404" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D404">
         <v>3.13</v>
@@ -27370,7 +27305,7 @@
         <v>25</v>
       </c>
       <c r="H404" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.45">
@@ -27381,10 +27316,10 @@
         <v>312</v>
       </c>
       <c r="C407" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H407" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.45">
@@ -27395,10 +27330,10 @@
         <v>312</v>
       </c>
       <c r="C408" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H408" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.45">
@@ -27409,10 +27344,10 @@
         <v>312</v>
       </c>
       <c r="C409" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H409" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.45">
@@ -27423,10 +27358,10 @@
         <v>312</v>
       </c>
       <c r="C410" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="H410" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.45">
@@ -27437,10 +27372,10 @@
         <v>312</v>
       </c>
       <c r="C411" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H411" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.45">
@@ -27451,10 +27386,10 @@
         <v>312</v>
       </c>
       <c r="C412" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="H412" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.45">
@@ -27465,10 +27400,10 @@
         <v>312</v>
       </c>
       <c r="C413" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H413" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.45">
@@ -27479,10 +27414,10 @@
         <v>312</v>
       </c>
       <c r="C414" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H414" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.45">
@@ -27493,7 +27428,7 @@
         <v>312</v>
       </c>
       <c r="C415" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D415">
         <v>4.55</v>
@@ -27505,7 +27440,7 @@
         <v>15</v>
       </c>
       <c r="H415" t="s">
-        <v>541</v>
+        <v>575</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.45">
@@ -27516,7 +27451,7 @@
         <v>312</v>
       </c>
       <c r="C416" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D416">
         <v>2.2799999999999998</v>
@@ -27528,7 +27463,7 @@
         <v>15</v>
       </c>
       <c r="H416" t="s">
-        <v>543</v>
+        <v>576</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.45">
@@ -27539,7 +27474,7 @@
         <v>312</v>
       </c>
       <c r="C417" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D417">
         <v>2.62</v>
@@ -27551,10 +27486,10 @@
         <v>25</v>
       </c>
       <c r="H417" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="I417" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.45">
@@ -27565,7 +27500,7 @@
         <v>312</v>
       </c>
       <c r="C418" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D418">
         <v>2.62</v>
@@ -27577,7 +27512,7 @@
         <v>25</v>
       </c>
       <c r="H418" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.45">
@@ -27588,10 +27523,10 @@
         <v>312</v>
       </c>
       <c r="C420" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H420" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.45">
@@ -27602,10 +27537,10 @@
         <v>312</v>
       </c>
       <c r="C421" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H421" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.45">
@@ -27616,10 +27551,10 @@
         <v>312</v>
       </c>
       <c r="C422" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="H422" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.45">
@@ -27630,10 +27565,10 @@
         <v>312</v>
       </c>
       <c r="C423" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H423" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.45">
@@ -27644,10 +27579,10 @@
         <v>312</v>
       </c>
       <c r="C424" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="H424" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.45">
@@ -27658,10 +27593,10 @@
         <v>312</v>
       </c>
       <c r="C425" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H425" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.45">
@@ -27672,10 +27607,10 @@
         <v>312</v>
       </c>
       <c r="C426" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H426" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.45">
@@ -27686,7 +27621,7 @@
         <v>312</v>
       </c>
       <c r="C427" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="D427">
         <v>10</v>
@@ -27698,7 +27633,7 @@
         <v>10</v>
       </c>
       <c r="H427" t="s">
-        <v>551</v>
+        <v>579</v>
       </c>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.45">
@@ -27709,7 +27644,7 @@
         <v>312</v>
       </c>
       <c r="C428" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D428">
         <v>5.77</v>
@@ -27721,10 +27656,10 @@
         <v>25</v>
       </c>
       <c r="H428" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="I428" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.45">
@@ -27735,7 +27670,7 @@
         <v>312</v>
       </c>
       <c r="C429" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D429">
         <v>5.77</v>
@@ -27747,7 +27682,7 @@
         <v>25</v>
       </c>
       <c r="H429" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.45">
@@ -27758,13 +27693,13 @@
         <v>312</v>
       </c>
       <c r="C431" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H431" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="I431" t="s">
-        <v>566</v>
+        <v>581</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.45">
@@ -27775,7 +27710,7 @@
         <v>312</v>
       </c>
       <c r="C432" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="D432">
         <v>4.55</v>
@@ -27787,7 +27722,7 @@
         <v>15</v>
       </c>
       <c r="H432" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.45">
@@ -27798,7 +27733,7 @@
         <v>312</v>
       </c>
       <c r="C433" t="s">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="D433">
         <v>2.62</v>
@@ -27810,10 +27745,10 @@
         <v>25</v>
       </c>
       <c r="H433" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="I433" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.45">
@@ -27824,7 +27759,7 @@
         <v>312</v>
       </c>
       <c r="C434" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="D434">
         <v>2.62</v>
@@ -27836,7 +27771,7 @@
         <v>25</v>
       </c>
       <c r="H434" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.45">
@@ -27847,13 +27782,13 @@
         <v>312</v>
       </c>
       <c r="C436" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H436" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="I436" t="s">
-        <v>566</v>
+        <v>581</v>
       </c>
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.45">
@@ -27864,7 +27799,7 @@
         <v>312</v>
       </c>
       <c r="C437" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="D437">
         <v>10</v>
@@ -27876,7 +27811,7 @@
         <v>10</v>
       </c>
       <c r="H437" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.45">
@@ -27887,7 +27822,7 @@
         <v>312</v>
       </c>
       <c r="C438" t="s">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="D438">
         <v>5.77</v>
@@ -27899,10 +27834,10 @@
         <v>25</v>
       </c>
       <c r="H438" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="I438" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.45">
@@ -27913,7 +27848,7 @@
         <v>312</v>
       </c>
       <c r="C439" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="D439">
         <v>5.77</v>
@@ -27925,7 +27860,7 @@
         <v>25</v>
       </c>
       <c r="H439" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.45">
@@ -27936,13 +27871,13 @@
         <v>312</v>
       </c>
       <c r="C441" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H441" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="I441" t="s">
-        <v>566</v>
+        <v>581</v>
       </c>
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.45">
@@ -27953,7 +27888,7 @@
         <v>312</v>
       </c>
       <c r="C442" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="D442">
         <v>220</v>
@@ -27965,7 +27900,7 @@
         <v>1</v>
       </c>
       <c r="H442" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.45">
@@ -27976,7 +27911,7 @@
         <v>312</v>
       </c>
       <c r="C443" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D443">
         <v>5.77</v>
@@ -27988,7 +27923,7 @@
         <v>25</v>
       </c>
       <c r="H443" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.45">
@@ -27999,7 +27934,7 @@
         <v>312</v>
       </c>
       <c r="C444" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D444">
         <v>5.77</v>
@@ -28011,10 +27946,10 @@
         <v>25</v>
       </c>
       <c r="H444" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="I444" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.45">
@@ -28025,13 +27960,13 @@
         <v>312</v>
       </c>
       <c r="C446" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H446" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="I446" t="s">
-        <v>566</v>
+        <v>581</v>
       </c>
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.45">
@@ -28042,7 +27977,7 @@
         <v>312</v>
       </c>
       <c r="C447" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="D447">
         <v>5</v>
@@ -28054,7 +27989,7 @@
         <v>1</v>
       </c>
       <c r="H447" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.45">
@@ -28065,7 +28000,7 @@
         <v>312</v>
       </c>
       <c r="C448" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="D448">
         <v>0.28999999999999998</v>
@@ -28077,7 +28012,7 @@
         <v>30</v>
       </c>
       <c r="H448" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.45">
@@ -28088,7 +28023,7 @@
         <v>312</v>
       </c>
       <c r="C449" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="D449">
         <v>0.28999999999999998</v>
@@ -28100,7 +28035,7 @@
         <v>30</v>
       </c>
       <c r="H449" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
     </row>
   </sheetData>
@@ -28119,60 +28054,60 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="B1" t="s">
-        <v>572</v>
+        <v>587</v>
       </c>
       <c r="C1" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="B2" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="C2" t="s">
-        <v>576</v>
+        <v>591</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="B3" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="C3" t="s">
-        <v>579</v>
+        <v>594</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="B4" t="s">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="C4" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>583</v>
+        <v>598</v>
       </c>
       <c r="B5" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="C5" t="s">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="D5" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
@@ -28180,35 +28115,35 @@
         <v>315</v>
       </c>
       <c r="B6" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
       <c r="C6" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>588</v>
+        <v>604</v>
       </c>
       <c r="B7" t="s">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="C7" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="D7" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="B9" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="C9" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
@@ -28216,26 +28151,26 @@
         <v>317</v>
       </c>
       <c r="B10" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="C10" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="B11" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="C11" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
